--- a/space-battleship/config_excel/jewel.xlsx
+++ b/space-battleship/config_excel/jewel.xlsx
@@ -164,7 +164,7 @@
     <t>para1表示可用的装备,0为全部,1为武器,2为防御,镶嵌到对应的武器上时,固定增加该武器para2暴击,并使该武器暴击率(包括这颗宝石附加的)*(1+para4*等级)</t>
   </si>
   <si>
-    <t>镶嵌到对应的武器上时,该武器固定增加{para2}暴击,并使该武器来自所有来源的暴击率提升{para4*等级,百分比}</t>
+    <t>镶嵌到对应的武器上时,该武器固定增加{para2,百分比}暴击,并使该武器来自所有来源的暴击率提升{para4*等级,百分比}</t>
   </si>
   <si>
     <t>蓄能宝石</t>

--- a/space-battleship/config_excel/jewel.xlsx
+++ b/space-battleship/config_excel/jewel.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\space-battleship\config_excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="jewel" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
   <si>
     <t>id</t>
   </si>
@@ -122,24 +127,6 @@
     <t>镶嵌到对应防御时,使该防御的效果(护盾,生命)提高{para2*等级*log10(承受攻击次数),整数百分比}</t>
   </si>
   <si>
-    <t>吸铁宝石</t>
-  </si>
-  <si>
-    <t>para1表示可用的装备,0为全部,1为武器,2为防御,镶嵌到武器上时,击杀该敌人时获得的铁额外*(1+para2*等级*该武器命中该敌人次数)</t>
-  </si>
-  <si>
-    <t>镶嵌到对应武器时,该武器命中敌人后使该敌人被击杀时额外掉落{para2*等级,整数百分比}的铁,每次命中叠加一次该效果,最多{para4}次</t>
-  </si>
-  <si>
-    <t>电子战宝石</t>
-  </si>
-  <si>
-    <t>para1表示可用的装备,0为全部,1为武器,2为防御,武器命中有para2的概率使该敌人进入电子干扰状态,电子干扰状态的敌人受到的伤害提高(1+para4*等级),并且死亡时会爆炸,对上下两格的敌人造成自身最大生命*para5*等级的伤害,para3为合成需要的宝石碎片数</t>
-  </si>
-  <si>
-    <t>镶嵌到对应武器时,武器命中有{para2,百分比}的概率使该敌人进入电子干扰状态,电子干扰状态的敌人受到的伤害提高{para4*等级,百分比},并且死亡时会爆炸,对上下两格的敌人造成自身最大生命{para5*等级,百分比}的伤害</t>
-  </si>
-  <si>
     <t>自动维修宝石</t>
   </si>
   <si>
@@ -165,24 +152,6 @@
   </si>
   <si>
     <t>镶嵌到对应的武器上时,该武器固定增加{para2,百分比}暴击,并使该武器来自所有来源的暴击率提升{para4*等级,百分比}</t>
-  </si>
-  <si>
-    <t>蓄能宝石</t>
-  </si>
-  <si>
-    <t>para1表示可用的装备,0为全部,1为武器,2为防御,镶嵌到对应的防御上时,该防御每受到para4次伤害,便立即使一个随机武器的CD立即结束,且这次武器的伤害*(1+para2*等级)</t>
-  </si>
-  <si>
-    <t>镶嵌到对应的防御上时,该防御每受到{para4}次伤害,便立即使一个随机武器的CD立即结束,且这次武器的伤害提高{para2*等级,百分比}</t>
-  </si>
-  <si>
-    <t>抗性宝石</t>
-  </si>
-  <si>
-    <t>para1表示可用的装备,0为全部,1为武器,2为防御,镶嵌到对应的防御上时,该防御的数值部分受到伤害时(仅限于该防御的部分,例如有2个护盾,只有装了该宝石的护盾那部分会有效),该伤害-该防御最大值*para2*等级</t>
-  </si>
-  <si>
-    <t>镶嵌到对应的防御上时,该防御受到伤害时,固定减免其最大值的{para2*等级,百分比}</t>
   </si>
   <si>
     <t>坚韧宝石</t>
@@ -1122,10 +1091,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="3" width="11.5" customWidth="1"/>
+    <col min="4" max="4" width="124.444444444444" customWidth="1"/>
     <col min="9" max="9" width="11.5"/>
   </cols>
   <sheetData>
@@ -1248,7 +1218,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1274,7 +1244,7 @@
         <v>30</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -1300,19 +1270,19 @@
         <v>33</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="H6">
         <v>1000</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1329,7 +1299,7 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1341,10 +1311,7 @@
         <v>1000</v>
       </c>
       <c r="I7">
-        <v>0.25</v>
-      </c>
-      <c r="J7">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1361,19 +1328,19 @@
         <v>39</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H8">
         <v>1000</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1390,128 +1357,15 @@
         <v>42</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="H9">
-        <v>1000</v>
-      </c>
-      <c r="I9">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10">
-        <v>10</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>0.1</v>
-      </c>
-      <c r="H10">
-        <v>1000</v>
-      </c>
-      <c r="I10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11">
-        <v>10</v>
-      </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="G11">
-        <v>0.6</v>
-      </c>
-      <c r="H11">
-        <v>1000</v>
-      </c>
-      <c r="I11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12">
-        <v>10</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12">
-        <v>0.005</v>
-      </c>
-      <c r="H12">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13">
-        <v>10</v>
-      </c>
-      <c r="B13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13">
-        <v>10</v>
-      </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
-      <c r="G13">
-        <v>0.05</v>
-      </c>
-      <c r="H13">
         <v>1000</v>
       </c>
     </row>
